--- a/manufacturing_forms/006_production_capacity_expansion_request_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/006_production_capacity_expansion_request_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>production_capacity_expansion_request_form</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Production Capacity Expansion Request Form</t>
+          <t>Timeline</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>timeline</t>
+          <t>review_approvals</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Timeline</t>
+          <t>Review and Approvals</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>review_approvals</t>
+          <t>approval</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Review and Approvals</t>
+          <t>Approval</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>production_capacity_expansion_request_form</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Production Capacity Expansion Request Form</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>approval</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Resources</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>production_capacity_expansion_request_form</t>
+          <t>production_plan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Production Capacity Expansion Request Form</t>
+          <t>Production Plan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>production_capacity_expansion_request_form</t>
+          <t>expected_completion_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Production Capacity Expansion Request Form</t>
+          <t>Expected Completion Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,16 +750,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>production_capacity_expansion_request_form</t>
+          <t>review_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Production Capacity Expansion Request Form</t>
+          <t>Review Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>final_notes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Final Notes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -826,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>review_approvals_choices</t>
+          <t>approval_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -860,29 +883,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>approval_choices</t>
+          <t>review_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Internal Review</t>
         </is>
       </c>
     </row>
@@ -894,29 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>external_review</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>review_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Option 2</t>
+          <t>External Review</t>
         </is>
       </c>
     </row>
